--- a/Outputs/Scenarios/PtX_demand_PT_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_PT_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0004653717633502872</v>
       </c>
       <c r="K16" t="n">
-        <v>0.005962405978116844</v>
+        <v>0.003243106961512187</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001987468659372282</v>
+        <v>0.004685965434744453</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>6.705219367598594e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001987468659372282</v>
+        <v>0.002008270900604766</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0006889262383035935</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03217364604717608</v>
+        <v>0.0175000789707683</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.01072454868239203</v>
+        <v>0.02528586510883428</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>3.625927570018914e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01072454868239203</v>
+        <v>0.01083679933235755</v>
       </c>
     </row>
     <row r="43">
